--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/73.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/73.xlsx
@@ -426,13 +426,13 @@
         <v>-6.870287536062911</v>
       </c>
       <c r="E2">
-        <v>-28.38839428680204</v>
+        <v>-33.75467221368347</v>
       </c>
       <c r="F2">
-        <v>-6.070370758203379</v>
+        <v>-6.919577229724263</v>
       </c>
       <c r="G2">
-        <v>-18.87855592618478</v>
+        <v>-21.50568899705652</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.375782965763943</v>
       </c>
       <c r="E3">
-        <v>-29.77081060407158</v>
+        <v>-34.43876387541519</v>
       </c>
       <c r="F3">
-        <v>-5.827792147576645</v>
+        <v>-7.470868426300565</v>
       </c>
       <c r="G3">
-        <v>-18.52608710843689</v>
+        <v>-20.90916841742632</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.000455763582462</v>
       </c>
       <c r="E4">
-        <v>-30.59302072303725</v>
+        <v>-32.81399268620314</v>
       </c>
       <c r="F4">
-        <v>-5.62459713565506</v>
+        <v>-7.097696634033738</v>
       </c>
       <c r="G4">
-        <v>-17.55563047850939</v>
+        <v>-21.29681178152897</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.794315260285379</v>
       </c>
       <c r="E5">
-        <v>-30.96984636640052</v>
+        <v>-34.17402475645277</v>
       </c>
       <c r="F5">
-        <v>-5.613246715359105</v>
+        <v>-6.818492844480073</v>
       </c>
       <c r="G5">
-        <v>-18.42093921629132</v>
+        <v>-21.07790526829021</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.731411842432684</v>
       </c>
       <c r="E6">
-        <v>-31.72915598139964</v>
+        <v>-35.37381450970398</v>
       </c>
       <c r="F6">
-        <v>-5.933156102130831</v>
+        <v>-7.198807150425532</v>
       </c>
       <c r="G6">
-        <v>-18.48616027396051</v>
+        <v>-20.87941323411935</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.79822457490756</v>
       </c>
       <c r="E7">
-        <v>-31.21064570752138</v>
+        <v>-35.56008196682448</v>
       </c>
       <c r="F7">
-        <v>-5.610243217090474</v>
+        <v>-6.806667708335965</v>
       </c>
       <c r="G7">
-        <v>-17.39204318123184</v>
+        <v>-20.55760834442896</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.964912952471077</v>
       </c>
       <c r="E8">
-        <v>-32.02959306096452</v>
+        <v>-36.2073299640298</v>
       </c>
       <c r="F8">
-        <v>-5.662758113393489</v>
+        <v>-7.13117538523317</v>
       </c>
       <c r="G8">
-        <v>-17.87856591950145</v>
+        <v>-20.41225553198172</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.200471685069547</v>
       </c>
       <c r="E9">
-        <v>-31.91145875952643</v>
+        <v>-36.34211999286811</v>
       </c>
       <c r="F9">
-        <v>-5.472189196882745</v>
+        <v>-6.883752614137586</v>
       </c>
       <c r="G9">
-        <v>-17.58613384510824</v>
+        <v>-20.33998466758666</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.467367642976031</v>
       </c>
       <c r="E10">
-        <v>-32.2626034267922</v>
+        <v>-37.07724076395526</v>
       </c>
       <c r="F10">
-        <v>-5.459594775590213</v>
+        <v>-6.494946081147061</v>
       </c>
       <c r="G10">
-        <v>-17.34872303757771</v>
+        <v>-21.25422492371179</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.73487670833421</v>
       </c>
       <c r="E11">
-        <v>-32.3026894787081</v>
+        <v>-36.49875085184541</v>
       </c>
       <c r="F11">
-        <v>-5.466047585342671</v>
+        <v>-6.622583275695987</v>
       </c>
       <c r="G11">
-        <v>-17.86851344797145</v>
+        <v>-20.70304557578745</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.969735049632473</v>
       </c>
       <c r="E12">
-        <v>-33.07657851577491</v>
+        <v>-36.27254904668827</v>
       </c>
       <c r="F12">
-        <v>-5.288678857637114</v>
+        <v>-6.386158154403694</v>
       </c>
       <c r="G12">
-        <v>-17.46357910451719</v>
+        <v>-20.74105229385106</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.147042204040678</v>
       </c>
       <c r="E13">
-        <v>-34.27639770410718</v>
+        <v>-37.82196642841268</v>
       </c>
       <c r="F13">
-        <v>-5.345471343617731</v>
+        <v>-6.610092191214438</v>
       </c>
       <c r="G13">
-        <v>-16.4212786705692</v>
+        <v>-20.06009790551452</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.254168929476497</v>
       </c>
       <c r="E14">
-        <v>-34.39596979604271</v>
+        <v>-37.69693978953491</v>
       </c>
       <c r="F14">
-        <v>-5.466411045850264</v>
+        <v>-6.834758692011072</v>
       </c>
       <c r="G14">
-        <v>-15.83392002571893</v>
+        <v>-20.64919789731844</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.282370462299776</v>
       </c>
       <c r="E15">
-        <v>-35.0614494296029</v>
+        <v>-37.98585190275027</v>
       </c>
       <c r="F15">
-        <v>-5.145805620328702</v>
+        <v>-6.467037619578708</v>
       </c>
       <c r="G15">
-        <v>-16.28960006647192</v>
+        <v>-19.47176430500294</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.233207668096382</v>
       </c>
       <c r="E16">
-        <v>-35.24319067695274</v>
+        <v>-38.192918640988</v>
       </c>
       <c r="F16">
-        <v>-5.555911018249494</v>
+        <v>-6.176749472322883</v>
       </c>
       <c r="G16">
-        <v>-15.65957345543876</v>
+        <v>-20.47461627830497</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.119450588708215</v>
       </c>
       <c r="E17">
-        <v>-35.54435684083285</v>
+        <v>-38.8108153339126</v>
       </c>
       <c r="F17">
-        <v>-5.079362030499398</v>
+        <v>-5.877626621617778</v>
       </c>
       <c r="G17">
-        <v>-15.41555645428462</v>
+        <v>-18.89638321391376</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.954319850590113</v>
       </c>
       <c r="E18">
-        <v>-35.3529790007947</v>
+        <v>-38.56779477629097</v>
       </c>
       <c r="F18">
-        <v>-5.070696783583071</v>
+        <v>-6.337492455328156</v>
       </c>
       <c r="G18">
-        <v>-15.71221444005871</v>
+        <v>-18.87157067509692</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.75587287183193</v>
       </c>
       <c r="E19">
-        <v>-36.60697005944371</v>
+        <v>-39.06104975062845</v>
       </c>
       <c r="F19">
-        <v>-4.822859477464121</v>
+        <v>-6.098058688723007</v>
       </c>
       <c r="G19">
-        <v>-15.14739564451257</v>
+        <v>-18.98029726697043</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.546753767423651</v>
       </c>
       <c r="E20">
-        <v>-37.02962838823861</v>
+        <v>-39.67806565535855</v>
       </c>
       <c r="F20">
-        <v>-4.692450797563175</v>
+        <v>-5.372972396839336</v>
       </c>
       <c r="G20">
-        <v>-14.4327647316778</v>
+        <v>-17.78679428660731</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.342972549829969</v>
       </c>
       <c r="E21">
-        <v>-37.51891641934537</v>
+        <v>-39.4677406800723</v>
       </c>
       <c r="F21">
-        <v>-4.857979739844906</v>
+        <v>-5.777344779346237</v>
       </c>
       <c r="G21">
-        <v>-15.20981101483722</v>
+        <v>-18.50871502071956</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.15910921739738</v>
       </c>
       <c r="E22">
-        <v>-37.52615518504663</v>
+        <v>-39.61822413558419</v>
       </c>
       <c r="F22">
-        <v>-4.481080695706091</v>
+        <v>-5.647523654339919</v>
       </c>
       <c r="G22">
-        <v>-14.23711480085241</v>
+        <v>-17.80242668264375</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.010063252430152</v>
       </c>
       <c r="E23">
-        <v>-37.5672261800592</v>
+        <v>-41.27342214165377</v>
       </c>
       <c r="F23">
-        <v>-4.487292782159403</v>
+        <v>-5.454583138220804</v>
       </c>
       <c r="G23">
-        <v>-14.8362904380051</v>
+        <v>-18.26117559911164</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.899577585456166</v>
       </c>
       <c r="E24">
-        <v>-38.80409960695923</v>
+        <v>-42.99396149918004</v>
       </c>
       <c r="F24">
-        <v>-4.101585165718914</v>
+        <v>-5.745581181653225</v>
       </c>
       <c r="G24">
-        <v>-14.13745744848373</v>
+        <v>-17.44612259788861</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.828969584815793</v>
       </c>
       <c r="E25">
-        <v>-39.97519694889784</v>
+        <v>-41.46859257867336</v>
       </c>
       <c r="F25">
-        <v>-3.958734892146276</v>
+        <v>-5.877975828772133</v>
       </c>
       <c r="G25">
-        <v>-14.71878593463421</v>
+        <v>-17.64647184810699</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.800750886396797</v>
       </c>
       <c r="E26">
-        <v>-38.40310096934301</v>
+        <v>-41.77052631889777</v>
       </c>
       <c r="F26">
-        <v>-4.081173572027772</v>
+        <v>-5.429932755646989</v>
       </c>
       <c r="G26">
-        <v>-14.29703567511322</v>
+        <v>-17.4437025890994</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.808341234818358</v>
       </c>
       <c r="E27">
-        <v>-38.64353803254326</v>
+        <v>-41.7341717295642</v>
       </c>
       <c r="F27">
-        <v>-4.296327147316841</v>
+        <v>-5.560715190143979</v>
       </c>
       <c r="G27">
-        <v>-14.62754895484466</v>
+        <v>-17.79645280321813</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.845683828427808</v>
       </c>
       <c r="E28">
-        <v>-37.95327179650209</v>
+        <v>-42.58538219607498</v>
       </c>
       <c r="F28">
-        <v>-4.049909633551082</v>
+        <v>-5.708403685288284</v>
       </c>
       <c r="G28">
-        <v>-14.24609300035491</v>
+        <v>-16.77158404680718</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.90901650821818</v>
       </c>
       <c r="E29">
-        <v>-39.03243885184799</v>
+        <v>-41.65541024538579</v>
       </c>
       <c r="F29">
-        <v>-4.303072942663655</v>
+        <v>-5.075927764221768</v>
       </c>
       <c r="G29">
-        <v>-14.71432994033835</v>
+        <v>-17.35221566312164</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.987017833197442</v>
       </c>
       <c r="E30">
-        <v>-38.72911034162921</v>
+        <v>-41.12584823069182</v>
       </c>
       <c r="F30">
-        <v>-4.055462106490613</v>
+        <v>-5.358608976039259</v>
       </c>
       <c r="G30">
-        <v>-14.33033314214721</v>
+        <v>-18.46264050317675</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.069548288098356</v>
       </c>
       <c r="E31">
-        <v>-38.11741312962111</v>
+        <v>-42.20913393314769</v>
       </c>
       <c r="F31">
-        <v>-4.406456472970585</v>
+        <v>-5.333686987900945</v>
       </c>
       <c r="G31">
-        <v>-15.15090978860251</v>
+        <v>-18.0449820779423</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.148493388627939</v>
       </c>
       <c r="E32">
-        <v>-38.08851693697817</v>
+        <v>-40.97908491657723</v>
       </c>
       <c r="F32">
-        <v>-4.287883619228675</v>
+        <v>-5.29633053276756</v>
       </c>
       <c r="G32">
-        <v>-14.97294313677514</v>
+        <v>-17.1537070762231</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.209872543696094</v>
       </c>
       <c r="E33">
-        <v>-38.46753209752414</v>
+        <v>-41.70947116808936</v>
       </c>
       <c r="F33">
-        <v>-4.419873629486188</v>
+        <v>-5.718590873589349</v>
       </c>
       <c r="G33">
-        <v>-15.06518155659031</v>
+        <v>-18.34295931611379</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.241775683757146</v>
       </c>
       <c r="E34">
-        <v>-37.75379478070121</v>
+        <v>-40.3834864296664</v>
       </c>
       <c r="F34">
-        <v>-3.986404610047876</v>
+        <v>-5.254316398536867</v>
       </c>
       <c r="G34">
-        <v>-14.58823788183859</v>
+        <v>-17.96447788679107</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.235937101089114</v>
       </c>
       <c r="E35">
-        <v>-37.0854690012272</v>
+        <v>-40.67493675256306</v>
       </c>
       <c r="F35">
-        <v>-4.416637326447987</v>
+        <v>-5.312062275478578</v>
       </c>
       <c r="G35">
-        <v>-15.54807924749441</v>
+        <v>-18.84718188610911</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.182149854310322</v>
       </c>
       <c r="E36">
-        <v>-36.78374130657013</v>
+        <v>-40.67056224667165</v>
       </c>
       <c r="F36">
-        <v>-4.172086210103574</v>
+        <v>-5.323383397215096</v>
       </c>
       <c r="G36">
-        <v>-15.09900374509228</v>
+        <v>-17.56589979077221</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.074106680745355</v>
       </c>
       <c r="E37">
-        <v>-37.43844543622907</v>
+        <v>-41.60739030700846</v>
       </c>
       <c r="F37">
-        <v>-4.208638934484874</v>
+        <v>-5.495243995746755</v>
       </c>
       <c r="G37">
-        <v>-15.44311012480797</v>
+        <v>-18.14066346511832</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.912187605007485</v>
       </c>
       <c r="E38">
-        <v>-36.67499906022394</v>
+        <v>-40.45056445090501</v>
       </c>
       <c r="F38">
-        <v>-4.161975831539409</v>
+        <v>-5.42746692553665</v>
       </c>
       <c r="G38">
-        <v>-14.76701727259585</v>
+        <v>-17.63296978812507</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.698211961139789</v>
       </c>
       <c r="E39">
-        <v>-36.51809422856918</v>
+        <v>-39.36964487611814</v>
       </c>
       <c r="F39">
-        <v>-4.106908793153663</v>
+        <v>-5.55671791641341</v>
       </c>
       <c r="G39">
-        <v>-15.46175180673961</v>
+        <v>-18.48575142158641</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.436837578642354</v>
       </c>
       <c r="E40">
-        <v>-36.3453646444946</v>
+        <v>-39.669475140166</v>
       </c>
       <c r="F40">
-        <v>-3.972251822134552</v>
+        <v>-5.286768116450136</v>
       </c>
       <c r="G40">
-        <v>-15.28603136006063</v>
+        <v>-17.61453004947133</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.137337569328054</v>
       </c>
       <c r="E41">
-        <v>-35.82907558711711</v>
+        <v>-39.49355977462704</v>
       </c>
       <c r="F41">
-        <v>-4.13286810866659</v>
+        <v>-4.99208399749953</v>
       </c>
       <c r="G41">
-        <v>-15.68022960433104</v>
+        <v>-18.79060300757019</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.809346292043258</v>
       </c>
       <c r="E42">
-        <v>-34.87275471041428</v>
+        <v>-38.73823521675466</v>
       </c>
       <c r="F42">
-        <v>-4.173791861374502</v>
+        <v>-5.133618211456437</v>
       </c>
       <c r="G42">
-        <v>-16.05367569388853</v>
+        <v>-18.1105838483485</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.461246392367119</v>
       </c>
       <c r="E43">
-        <v>-34.60547285329656</v>
+        <v>-38.82175386287813</v>
       </c>
       <c r="F43">
-        <v>-3.835594630544239</v>
+        <v>-4.963608173286971</v>
       </c>
       <c r="G43">
-        <v>-15.50755320427542</v>
+        <v>-18.13021372812361</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.103334359547028</v>
       </c>
       <c r="E44">
-        <v>-34.44170738352017</v>
+        <v>-38.81818316112308</v>
       </c>
       <c r="F44">
-        <v>-3.8262460145254</v>
+        <v>-5.246327394046433</v>
       </c>
       <c r="G44">
-        <v>-15.87215020560644</v>
+        <v>-18.46683496437501</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.745425341297782</v>
       </c>
       <c r="E45">
-        <v>-33.69153396483153</v>
+        <v>-37.71701904328492</v>
       </c>
       <c r="F45">
-        <v>-3.809750133710183</v>
+        <v>-5.407741076506894</v>
       </c>
       <c r="G45">
-        <v>-15.66053516891791</v>
+        <v>-18.86858125247496</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.392560701358515</v>
       </c>
       <c r="E46">
-        <v>-34.06380849181709</v>
+        <v>-37.92379822342316</v>
       </c>
       <c r="F46">
-        <v>-3.801039751175266</v>
+        <v>-5.277170066749616</v>
       </c>
       <c r="G46">
-        <v>-15.39008511690546</v>
+        <v>-18.42878189867386</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.050444933964403</v>
       </c>
       <c r="E47">
-        <v>-33.28439471646092</v>
+        <v>-38.67681552378863</v>
       </c>
       <c r="F47">
-        <v>-3.742376908508516</v>
+        <v>-4.985004040204558</v>
       </c>
       <c r="G47">
-        <v>-16.12971395910727</v>
+        <v>-18.73233078498794</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.72562762980167</v>
       </c>
       <c r="E48">
-        <v>-33.68442426063949</v>
+        <v>-38.17137442589651</v>
       </c>
       <c r="F48">
-        <v>-3.764229674582707</v>
+        <v>-4.836433420865353</v>
       </c>
       <c r="G48">
-        <v>-15.58513087316993</v>
+        <v>-18.16236574640101</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.419076363790214</v>
       </c>
       <c r="E49">
-        <v>-32.35124830549234</v>
+        <v>-37.00053747121334</v>
       </c>
       <c r="F49">
-        <v>-3.646655347420482</v>
+        <v>-4.999878998015323</v>
       </c>
       <c r="G49">
-        <v>-16.31932545486903</v>
+        <v>-17.8969940712458</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.132033043833762</v>
       </c>
       <c r="E50">
-        <v>-32.46772292120663</v>
+        <v>-36.48601904717285</v>
       </c>
       <c r="F50">
-        <v>-3.691806011216703</v>
+        <v>-4.797014980630064</v>
       </c>
       <c r="G50">
-        <v>-16.10284888205609</v>
+        <v>-18.64117491356411</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.867839838829181</v>
       </c>
       <c r="E51">
-        <v>-32.17212451611894</v>
+        <v>-36.5267300285018</v>
       </c>
       <c r="F51">
-        <v>-3.697730655046362</v>
+        <v>-4.452117881924535</v>
       </c>
       <c r="G51">
-        <v>-15.95185986582824</v>
+        <v>-17.40994661150823</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.62466034822064</v>
       </c>
       <c r="E52">
-        <v>-31.60453690518256</v>
+        <v>-36.28205431363037</v>
       </c>
       <c r="F52">
-        <v>-3.879086362394037</v>
+        <v>-5.192120307972771</v>
       </c>
       <c r="G52">
-        <v>-16.48269425614099</v>
+        <v>-18.21442738555159</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.401225167330054</v>
       </c>
       <c r="E53">
-        <v>-31.70054961109319</v>
+        <v>-35.89056094295626</v>
       </c>
       <c r="F53">
-        <v>-3.85109277663273</v>
+        <v>-5.211744799823939</v>
       </c>
       <c r="G53">
-        <v>-16.11533957037576</v>
+        <v>-18.86041744717511</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.199693882543938</v>
       </c>
       <c r="E54">
-        <v>-31.64651359499666</v>
+        <v>-35.01861685820135</v>
       </c>
       <c r="F54">
-        <v>-3.887929776225851</v>
+        <v>-4.753687954195472</v>
       </c>
       <c r="G54">
-        <v>-16.41184196050951</v>
+        <v>-18.02342711593611</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.017942123918957</v>
       </c>
       <c r="E55">
-        <v>-31.58992804803382</v>
+        <v>-36.17359962538367</v>
       </c>
       <c r="F55">
-        <v>-3.932292546329141</v>
+        <v>-5.136943202025903</v>
       </c>
       <c r="G55">
-        <v>-16.17287023075722</v>
+        <v>-18.17739893369484</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.8540497775475904</v>
       </c>
       <c r="E56">
-        <v>-30.36282480380534</v>
+        <v>-34.6647098217909</v>
       </c>
       <c r="F56">
-        <v>-3.891300694266864</v>
+        <v>-5.048078295698764</v>
       </c>
       <c r="G56">
-        <v>-16.28601640092566</v>
+        <v>-18.02951355391006</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.7095385895262266</v>
       </c>
       <c r="E57">
-        <v>-31.0770489315841</v>
+        <v>-35.67067862327681</v>
       </c>
       <c r="F57">
-        <v>-4.109452224853859</v>
+        <v>-5.109613189043165</v>
       </c>
       <c r="G57">
-        <v>-16.37077133254931</v>
+        <v>-20.05084327545948</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.5816736268183887</v>
       </c>
       <c r="E58">
-        <v>-29.19715710220192</v>
+        <v>-34.87355625031365</v>
       </c>
       <c r="F58">
-        <v>-3.773484851952535</v>
+        <v>-4.981743981577626</v>
       </c>
       <c r="G58">
-        <v>-16.40614120109088</v>
+        <v>-17.83289528851443</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.4665951145266065</v>
       </c>
       <c r="E59">
-        <v>-29.79262652760353</v>
+        <v>-34.52371578356208</v>
       </c>
       <c r="F59">
-        <v>-3.840888167566595</v>
+        <v>-5.363801947735984</v>
       </c>
       <c r="G59">
-        <v>-16.20472264466331</v>
+        <v>-19.41480636899978</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.3627539096259029</v>
       </c>
       <c r="E60">
-        <v>-29.81647573596493</v>
+        <v>-33.37249844251714</v>
       </c>
       <c r="F60">
-        <v>-3.892039493076417</v>
+        <v>-5.447389154099921</v>
       </c>
       <c r="G60">
-        <v>-16.34400226131876</v>
+        <v>-19.41838506872773</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.2651609252458363</v>
       </c>
       <c r="E61">
-        <v>-29.22992061164742</v>
+        <v>-34.89765905321947</v>
       </c>
       <c r="F61">
-        <v>-4.044279559021695</v>
+        <v>-5.291186655954212</v>
       </c>
       <c r="G61">
-        <v>-16.09656546662255</v>
+        <v>-18.94195287326182</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.1678581410645685</v>
       </c>
       <c r="E62">
-        <v>-29.18667368487417</v>
+        <v>-33.85349483771586</v>
       </c>
       <c r="F62">
-        <v>-3.79927075166772</v>
+        <v>-5.406666532043269</v>
       </c>
       <c r="G62">
-        <v>-16.57079449403207</v>
+        <v>-18.83853474116053</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.06864962924499962</v>
       </c>
       <c r="E63">
-        <v>-28.43106156890231</v>
+        <v>-32.58351600158276</v>
       </c>
       <c r="F63">
-        <v>-3.751701768938623</v>
+        <v>-5.687140057814637</v>
       </c>
       <c r="G63">
-        <v>-16.68350036164379</v>
+        <v>-19.48940454690894</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.03569700697693159</v>
       </c>
       <c r="E64">
-        <v>-28.79184962156741</v>
+        <v>-33.399571924372</v>
       </c>
       <c r="F64">
-        <v>-4.253755548603913</v>
+        <v>-5.558744268132214</v>
       </c>
       <c r="G64">
-        <v>-16.95423677584539</v>
+        <v>-19.08443047690821</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.1483536123261861</v>
       </c>
       <c r="E65">
-        <v>-29.97442438087846</v>
+        <v>-34.3834485654115</v>
       </c>
       <c r="F65">
-        <v>-3.922543252713696</v>
+        <v>-5.236859208230978</v>
       </c>
       <c r="G65">
-        <v>-16.81224913293882</v>
+        <v>-19.56514320775639</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.2689154299151862</v>
       </c>
       <c r="E66">
-        <v>-28.0615335614024</v>
+        <v>-34.99990973207566</v>
       </c>
       <c r="F66">
-        <v>-4.050169361321214</v>
+        <v>-5.70715493317396</v>
       </c>
       <c r="G66">
-        <v>-16.8489266669684</v>
+        <v>-19.512591607866</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.3977802355679758</v>
       </c>
       <c r="E67">
-        <v>-28.44728709127179</v>
+        <v>-34.29498708990866</v>
       </c>
       <c r="F67">
-        <v>-4.286729097616321</v>
+        <v>-5.703693743895768</v>
       </c>
       <c r="G67">
-        <v>-16.69606553723809</v>
+        <v>-18.98630259657867</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.5366990479362633</v>
       </c>
       <c r="E68">
-        <v>-29.66110379276176</v>
+        <v>-33.59668507674088</v>
       </c>
       <c r="F68">
-        <v>-4.106292731552558</v>
+        <v>-5.757932504087738</v>
       </c>
       <c r="G68">
-        <v>-15.87562627842267</v>
+        <v>-18.98086999134873</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.6847212380774089</v>
       </c>
       <c r="E69">
-        <v>-28.82442293510459</v>
+        <v>-33.80060905401728</v>
       </c>
       <c r="F69">
-        <v>-4.290506236224643</v>
+        <v>-5.563652172764161</v>
       </c>
       <c r="G69">
-        <v>-16.7927069826205</v>
+        <v>-19.99161430521638</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.8409195311484323</v>
       </c>
       <c r="E70">
-        <v>-28.6867527967974</v>
+        <v>-33.35430529819133</v>
       </c>
       <c r="F70">
-        <v>-4.458826460182336</v>
+        <v>-5.694788565533251</v>
       </c>
       <c r="G70">
-        <v>-16.31522699949141</v>
+        <v>-19.45620308569559</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.006074265783165</v>
       </c>
       <c r="E71">
-        <v>-28.83208964159957</v>
+        <v>-32.29556845333104</v>
       </c>
       <c r="F71">
-        <v>-4.073717484577884</v>
+        <v>-6.262426378642242</v>
       </c>
       <c r="G71">
-        <v>-17.06180467678016</v>
+        <v>-18.71119460699246</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.178429723502417</v>
       </c>
       <c r="E72">
-        <v>-29.26817716006422</v>
+        <v>-33.58645072548354</v>
       </c>
       <c r="F72">
-        <v>-4.497014360921328</v>
+        <v>-5.553819734588155</v>
       </c>
       <c r="G72">
-        <v>-16.33622413457424</v>
+        <v>-19.24234349913144</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.355666401853943</v>
       </c>
       <c r="E73">
-        <v>-28.28788027772779</v>
+        <v>-33.00865819837087</v>
       </c>
       <c r="F73">
-        <v>-4.712890106107837</v>
+        <v>-5.848686771571995</v>
       </c>
       <c r="G73">
-        <v>-16.55397361214704</v>
+        <v>-19.24647009414614</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.536902650550187</v>
       </c>
       <c r="E74">
-        <v>-29.43198338610668</v>
+        <v>-32.43206798110724</v>
       </c>
       <c r="F74">
-        <v>-4.667379149215853</v>
+        <v>-5.974070352603252</v>
       </c>
       <c r="G74">
-        <v>-16.22478124008576</v>
+        <v>-17.89174520129329</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.718310800297371</v>
       </c>
       <c r="E75">
-        <v>-29.35482498172698</v>
+        <v>-33.19759292668189</v>
       </c>
       <c r="F75">
-        <v>-4.679729679797408</v>
+        <v>-5.8742438257824</v>
       </c>
       <c r="G75">
-        <v>-15.73863424873486</v>
+        <v>-19.02229981349993</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.894438580406885</v>
       </c>
       <c r="E76">
-        <v>-30.24068053863345</v>
+        <v>-34.60221235201104</v>
       </c>
       <c r="F76">
-        <v>-4.765667897592814</v>
+        <v>-5.62603830803811</v>
       </c>
       <c r="G76">
-        <v>-16.23903810445063</v>
+        <v>-19.44235010788651</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.061026209833535</v>
       </c>
       <c r="E77">
-        <v>-29.32105162257778</v>
+        <v>-34.88963912575188</v>
       </c>
       <c r="F77">
-        <v>-4.808946620996985</v>
+        <v>-5.946104481695464</v>
       </c>
       <c r="G77">
-        <v>-15.85553292227207</v>
+        <v>-19.51508113811153</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.21217021154972</v>
       </c>
       <c r="E78">
-        <v>-29.87699652684044</v>
+        <v>-33.78986298519708</v>
       </c>
       <c r="F78">
-        <v>-4.91047404797102</v>
+        <v>-5.990913856866908</v>
       </c>
       <c r="G78">
-        <v>-15.62356961742641</v>
+        <v>-18.54035721498391</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.341158154975663</v>
       </c>
       <c r="E79">
-        <v>-30.53022890244689</v>
+        <v>-34.57056737564544</v>
       </c>
       <c r="F79">
-        <v>-4.793999604567068</v>
+        <v>-5.848017655822722</v>
       </c>
       <c r="G79">
-        <v>-15.86904160334506</v>
+        <v>-18.64303047433887</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.442665716282482</v>
       </c>
       <c r="E80">
-        <v>-31.22332996321687</v>
+        <v>-35.25970828589571</v>
       </c>
       <c r="F80">
-        <v>-5.401083968691345</v>
+        <v>-6.182477340692548</v>
       </c>
       <c r="G80">
-        <v>-14.9043668412019</v>
+        <v>-17.92397005157255</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.511007834913096</v>
       </c>
       <c r="E81">
-        <v>-30.92003768079015</v>
+        <v>-34.75976701968591</v>
       </c>
       <c r="F81">
-        <v>-5.068536608714411</v>
+        <v>-6.23235734627875</v>
       </c>
       <c r="G81">
-        <v>-14.87882929291197</v>
+        <v>-19.08348531615675</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.540304182200458</v>
       </c>
       <c r="E82">
-        <v>-30.39742913793495</v>
+        <v>-35.59235866531416</v>
       </c>
       <c r="F82">
-        <v>-4.970768107730673</v>
+        <v>-6.382298663087768</v>
       </c>
       <c r="G82">
-        <v>-15.8581697717941</v>
+        <v>-18.45323358802692</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.524193346986946</v>
       </c>
       <c r="E83">
-        <v>-31.63595319361077</v>
+        <v>-36.93708675765487</v>
       </c>
       <c r="F83">
-        <v>-5.259879165564848</v>
+        <v>-5.968768897051318</v>
       </c>
       <c r="G83">
-        <v>-15.02847422765087</v>
+        <v>-17.91632434664961</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.457175388691565</v>
       </c>
       <c r="E84">
-        <v>-33.31061910943933</v>
+        <v>-37.61922664708928</v>
       </c>
       <c r="F84">
-        <v>-5.110878570069601</v>
+        <v>-6.265511041839038</v>
       </c>
       <c r="G84">
-        <v>-15.06954485561107</v>
+        <v>-18.43526891265806</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.335248251603473</v>
       </c>
       <c r="E85">
-        <v>-33.18804011076271</v>
+        <v>-38.25067479848183</v>
       </c>
       <c r="F85">
-        <v>-4.913838631188371</v>
+        <v>-6.161244199557773</v>
       </c>
       <c r="G85">
-        <v>-15.13311560632892</v>
+        <v>-17.93219841251041</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.151241088135003</v>
       </c>
       <c r="E86">
-        <v>-34.11415606583436</v>
+        <v>-39.0013372923633</v>
       </c>
       <c r="F86">
-        <v>-5.02703242778849</v>
+        <v>-5.853051465074946</v>
       </c>
       <c r="G86">
-        <v>-15.44336338154172</v>
+        <v>-17.37650844628881</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.900381279671108</v>
       </c>
       <c r="E87">
-        <v>-34.43390255856796</v>
+        <v>-38.9293662549594</v>
       </c>
       <c r="F87">
-        <v>-5.172070591083307</v>
+        <v>-5.819823731263112</v>
       </c>
       <c r="G87">
-        <v>-14.8599873229752</v>
+        <v>-18.16450104827384</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.58243802412353</v>
       </c>
       <c r="E88">
-        <v>-35.18648965390269</v>
+        <v>-39.29425936931246</v>
       </c>
       <c r="F88">
-        <v>-5.205014049683322</v>
+        <v>-6.534720459286844</v>
       </c>
       <c r="G88">
-        <v>-15.0501202296594</v>
+        <v>-18.1374373384903</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.190978689502679</v>
       </c>
       <c r="E89">
-        <v>-36.48096979865429</v>
+        <v>-39.213104586621</v>
       </c>
       <c r="F89">
-        <v>-5.33744987315603</v>
+        <v>-5.937443194043926</v>
       </c>
       <c r="G89">
-        <v>-14.7479187353798</v>
+        <v>-17.69026871031878</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.7235852568987763</v>
       </c>
       <c r="E90">
-        <v>-37.82737342637784</v>
+        <v>-41.49600569607879</v>
       </c>
       <c r="F90">
-        <v>-5.486768001687323</v>
+        <v>-6.366327384857041</v>
       </c>
       <c r="G90">
-        <v>-14.67820857795936</v>
+        <v>-18.17144988336077</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.1862404059601855</v>
       </c>
       <c r="E91">
-        <v>-38.59570829007425</v>
+        <v>-42.68686529858687</v>
       </c>
       <c r="F91">
-        <v>-5.33031686171289</v>
+        <v>-6.785907303416948</v>
       </c>
       <c r="G91">
-        <v>-14.36766947473911</v>
+        <v>-17.58252866101597</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4250133825347268</v>
       </c>
       <c r="E92">
-        <v>-39.97602339540423</v>
+        <v>-42.83768386117534</v>
       </c>
       <c r="F92">
-        <v>-5.463934921651474</v>
+        <v>-6.103840007167318</v>
       </c>
       <c r="G92">
-        <v>-14.88466412942493</v>
+        <v>-18.1768179329527</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.108592411897329</v>
       </c>
       <c r="E93">
-        <v>-40.13938130251993</v>
+        <v>-45.07238162905848</v>
       </c>
       <c r="F93">
-        <v>-5.379890024277976</v>
+        <v>-5.981218409252588</v>
       </c>
       <c r="G93">
-        <v>-14.42281985287783</v>
+        <v>-18.22908317065394</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.851203316977384</v>
       </c>
       <c r="E94">
-        <v>-41.49320483490505</v>
+        <v>-46.51045968459331</v>
       </c>
       <c r="F94">
-        <v>-5.705498376786411</v>
+        <v>-5.95898238634686</v>
       </c>
       <c r="G94">
-        <v>-14.98996596193807</v>
+        <v>-18.97831093964687</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.650151106048195</v>
       </c>
       <c r="E95">
-        <v>-43.04114593410296</v>
+        <v>-46.06512275796799</v>
       </c>
       <c r="F95">
-        <v>-5.440253767097908</v>
+        <v>-6.649630597172821</v>
       </c>
       <c r="G95">
-        <v>-15.51427195644737</v>
+        <v>-18.38166124874064</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.5036922603443</v>
       </c>
       <c r="E96">
-        <v>-45.40300098788448</v>
+        <v>-48.81502274946678</v>
       </c>
       <c r="F96">
-        <v>-5.629314203724197</v>
+        <v>-6.251584327945143</v>
       </c>
       <c r="G96">
-        <v>-15.63085116234004</v>
+        <v>-18.08917951616434</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.384420507123568</v>
       </c>
       <c r="E97">
-        <v>-46.15578054336455</v>
+        <v>-49.70278366181198</v>
       </c>
       <c r="F97">
-        <v>-5.91044575930343</v>
+        <v>-6.30763326399846</v>
       </c>
       <c r="G97">
-        <v>-15.79198534537299</v>
+        <v>-18.40445601005129</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.301215723542348</v>
       </c>
       <c r="E98">
-        <v>-48.48074664787959</v>
+        <v>-51.21248519437062</v>
       </c>
       <c r="F98">
-        <v>-5.930349775248673</v>
+        <v>-6.475463726901804</v>
       </c>
       <c r="G98">
-        <v>-15.77005298117531</v>
+        <v>-18.43844703637576</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.217185806483711</v>
       </c>
       <c r="E99">
-        <v>-49.46106843682306</v>
+        <v>-52.72302336250218</v>
       </c>
       <c r="F99">
-        <v>-6.122419253114296</v>
+        <v>-6.169896380900298</v>
       </c>
       <c r="G99">
-        <v>-15.74565260527812</v>
+        <v>-19.52527430782695</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.148138842789932</v>
       </c>
       <c r="E100">
-        <v>-51.51353361792654</v>
+        <v>-52.93784850883355</v>
       </c>
       <c r="F100">
-        <v>-6.052517641418629</v>
+        <v>-6.053862999593795</v>
       </c>
       <c r="G100">
-        <v>-15.60738270501215</v>
+        <v>-18.3502690006645</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.018578630630985</v>
       </c>
       <c r="E101">
-        <v>-52.63520606242694</v>
+        <v>-54.68656176739854</v>
       </c>
       <c r="F101">
-        <v>-6.085415964400053</v>
+        <v>-6.171921148913187</v>
       </c>
       <c r="G101">
-        <v>-16.39617314847213</v>
+        <v>-19.15597633183017</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.917732853645797</v>
       </c>
       <c r="E102">
-        <v>-54.52138114949475</v>
+        <v>-56.30225676258071</v>
       </c>
       <c r="F102">
-        <v>-6.069704018012978</v>
+        <v>-6.54084425413537</v>
       </c>
       <c r="G102">
-        <v>-16.1980072030369</v>
+        <v>-19.00364819993168</v>
       </c>
     </row>
   </sheetData>
